--- a/config/Workset liste.xlsx
+++ b/config/Workset liste.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Revit\Python\Revit_BIM_Agent\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Revit\Python\Revit_BIM_Agent\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CADF217-7935-4BAD-957B-0375EE271863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0F0477-0309-49EF-8728-37BCC746D1C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="2100" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51480" yWindow="2100" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Familieunntak" sheetId="2" r:id="rId2"/>
+    <sheet name="BAS" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">BAS!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Familieunntak!$A$1:$D$3</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t>Type elementer</t>
   </si>
@@ -74,9 +80,6 @@
     <t>RIE xxx Spaces</t>
   </si>
   <si>
-    <t>RIE xxx Infononde</t>
-  </si>
-  <si>
     <t>Communication Devices</t>
   </si>
   <si>
@@ -99,6 +102,39 @@
   </si>
   <si>
     <t>RIE xxx Infonode</t>
+  </si>
+  <si>
+    <t>Modell</t>
+  </si>
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Familie</t>
+  </si>
+  <si>
+    <t>U_F_STA_FBU_RIE_XXX</t>
+  </si>
+  <si>
+    <t>Personheis</t>
+  </si>
+  <si>
+    <t>RIE xxx Rulletrapper og heiser</t>
+  </si>
+  <si>
+    <t>Rulletrapp</t>
+  </si>
+  <si>
+    <t>U_F_BAS_FBU_RIE_XXX</t>
+  </si>
+  <si>
+    <t>RIE xxx Heis</t>
+  </si>
+  <si>
+    <t>Vareheis</t>
+  </si>
+  <si>
+    <t>Lavfartheis</t>
   </si>
 </sst>
 </file>
@@ -122,12 +158,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -142,9 +184,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +495,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -460,18 +503,18 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -484,15 +527,15 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -500,7 +543,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -509,4 +552,136 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D523F76A-F93E-49A4-972E-A738AFD80EE1}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="38.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D3" xr:uid="{D523F76A-F93E-49A4-972E-A738AFD80EE1}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323ED0A9-D02B-418C-95D3-6D19E6510EE0}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="20.625" customWidth="1"/>
+    <col min="4" max="4" width="38.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D4" xr:uid="{323ED0A9-D02B-418C-95D3-6D19E6510EE0}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>